--- a/src/test/resources/app.VWO.xlsx
+++ b/src/test/resources/app.VWO.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\intelij Workspace\WebAutomation\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\Hp\VS-WorkSpace\Web-Automation_selenium_practice\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E95C5C-7FA5-4542-BB8C-F6754FEB792E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Signin1" sheetId="1" r:id="rId1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>Browser_Name</t>
   </si>
@@ -56,13 +57,37 @@
   </si>
   <si>
     <t>app_001</t>
+  </si>
+  <si>
+    <t>app_002</t>
+  </si>
+  <si>
+    <t>UserName@123</t>
+  </si>
+  <si>
+    <t>Password@123</t>
+  </si>
+  <si>
+    <t>FireFox</t>
+  </si>
+  <si>
+    <t>https://app.fireflink.com</t>
+  </si>
+  <si>
+    <t>2ndTest case password</t>
+  </si>
+  <si>
+    <t>2ndTest case Username</t>
+  </si>
+  <si>
+    <t>Wingify@1234</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,8 +107,16 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -106,6 +139,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -133,18 +172,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -422,52 +465,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" customWidth="1"/>
-    <col min="2" max="2" width="44.85546875" customWidth="1"/>
+    <col min="1" max="1" width="25.88671875" customWidth="1"/>
+    <col min="2" max="2" width="44.88671875" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -476,41 +535,54 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="40.21875" customWidth="1"/>
+    <col min="3" max="3" width="30.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
+      <c r="C2" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="praveen.m@fireflink.com"/>
-    <hyperlink ref="C2" r:id="rId2" display="Password@123"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{CF7B44F5-58A0-4A6A-8DFC-657012AD1653}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{EA54D5A7-F784-4E23-BA3A-DFC3BED3FF8C}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{ED2D30AB-A06D-4AE4-AD2B-96A5DDEA7DDD}"/>
+    <hyperlink ref="B2" r:id="rId4" xr:uid="{38CEDD71-2D2D-4263-BD54-89822D287AFF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
